--- a/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$not）.xlsx
+++ b/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$not）.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>name</t>
   </si>
@@ -55,106 +55,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>使用$isnull:0查询，目标字段存在且为null，走索引查询</t>
-  </si>
-  <si>
-    <t>使用$isnull:0查询，目标字段存在且不为null，走索引查询</t>
-  </si>
-  <si>
-    <t>使用$isnull:0查询，目标字段不存在</t>
-  </si>
-  <si>
-    <t>使用$isnull:1查询，目标字段存在且为null，走索引查询</t>
-  </si>
-  <si>
-    <t>使用$isnull:1查询，目标字段存在且不为null，不走索引查询</t>
-  </si>
-  <si>
-    <t>使用$isnull:1查询，目标字段存在且不为null，走索引查询</t>
-  </si>
-  <si>
-    <t>使用$isnull:1查询，目标字段不存在</t>
-  </si>
-  <si>
-    <t>选择集合中指定的“&lt;字段名&gt;”是否为空，或不存在。“0”代表期望该字段存在且不为 null；“1”代表期望该字段不存在或为 null。</t>
+    <t>1、查询成功，返回与匹配条件匹配的记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>使用$isnull:0查询，目标字段存在且为null，不走索引查询</t>
+    <t>1、查询成功，查看结果集包含所有记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、查询成功，返回字段存在且为null的记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$isnull: 0}}查询，目标字段存在且为null
+    <t>使用$not查询，走索引查询</t>
+  </si>
+  <si>
+    <t>1、find({$not:[{&lt;表达式1&gt;}，{&lt;表达式2&gt;},...,{&lt;表达式N&gt;}]})查询，目标字段覆盖所有数据类型（覆盖多层嵌套数组），取值个数覆盖：1个、多个
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$isnull: 0}}查询，目标字段存在且为null，且目标字段为索引字段
+  </si>
+  <si>
+    <t>使用$not查询，不走索引查询</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$not:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}})查询，目标字段为索引字段，且目标字段需要覆盖所有数据类型（覆盖多层嵌套数组），取值个数覆盖：1个、多个
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$isnull:0查询，目标字段存在且不为null，不走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$isnull: 0}}查询，目标字段存在且不为null
+  </si>
+  <si>
+    <t>使用$not查询，指定多个不同数据类型的值</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$not:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}})查询，$not指定多个值，且为不同类型的值
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、查询成功，只返回字段存在且为null的记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$isnull: 0}}查询，目标字段存在且不为null，且目标字段为索引字段
+  </si>
+  <si>
+    <t>使用$not查询，给定值为空（如{$not:[]}）</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$not:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}})查询，$not指定值为空，如{$not:[]}
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$isnull: 0}}查询，目标字段不存在
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$isnull: 1}}查询，目标字段存在且为null
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$isnull: 2}}查询，目标字段存在且为null，且目标字段为索引字段
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$isnull: 1}}查询，目标字段存在且不为null
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$isnull: 1}}查询，目标字段存在且不为null，且目标字段为索引字段
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$isnull: 1}}查询，目标字段不存在
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$isnull:1查询，目标字段存在且为null，不走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、查询成功，返回字段不存在或为 null的记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、查询成功，只返回字段不存在或为 null的记录</t>
+  </si>
+  <si>
+    <t>$not 是一个逻辑“非”操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -221,31 +158,31 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
@@ -304,34 +241,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I11" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I5" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I5"/>
   <tableColumns count="9">
-    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="0">
+    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="8">
+    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="7">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/summary" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="7">
+    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/preconditions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="6">
+    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="5">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/execution_type" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="5">
+    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="4">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/importance" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="4">
+    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="3">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/step_number" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="3">
+    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="2">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/actions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="2">
+    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="1">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/expectedresults" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="1">
+    <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="0">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/execution_type" xmlDataType="integer"/>
     </tableColumn>
   </tableColumns>
@@ -624,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -668,10 +605,10 @@
     </row>
     <row r="2" spans="1:9" ht="94.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -686,18 +623,18 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="40.5">
+    <row r="3" spans="1:9" ht="67.5">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -712,18 +649,18 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="40.5">
-      <c r="A4" s="1" t="s">
-        <v>22</v>
+      <c r="A4" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="1" t="s">
@@ -739,10 +676,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -750,7 +687,7 @@
     </row>
     <row r="5" spans="1:9" ht="40.5">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -765,168 +702,12 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="I5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="40.5">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="40.5">
-      <c r="A7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="40.5">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="40.5">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="40.5">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="40.5">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="3">
         <v>1</v>
       </c>
     </row>
